--- a/light-refract/files/R1_折射小測驗_Kahoot匯入.xlsx
+++ b/light-refract/files/R1_折射小測驗_Kahoot匯入.xlsx
@@ -507,7 +507,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>吸管放進水裡，看起來怎麼了？</t>
+          <t>🥤 吸管放進水裡，看起來怎麼了？</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -533,10 +533,8 @@
       <c r="G9" t="n">
         <v>30</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>把吸管拿出水面，吸管是？</t>
+          <t>🥤 把吸管拿出水面，吸管是？</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -561,10 +559,8 @@
       <c r="G10" t="n">
         <v>20</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -573,7 +569,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>吸管看起來斷掉，是誰在搞鬼？</t>
+          <t>🕵️ 吸管看起來斷掉，是誰在搞鬼？</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -599,10 +595,8 @@
       <c r="G11" t="n">
         <v>30</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +605,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光從空氣進到水裡，走路方向會？</t>
+          <t>💡 光從空氣進到水裡，走路方向會？</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -627,10 +621,8 @@
       <c r="G12" t="n">
         <v>20</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +631,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>光進到水裡會轉彎，這個叫做？</t>
+          <t>✨ 光進到水裡會轉彎，這個叫做？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -665,10 +657,8 @@
       <c r="G13" t="n">
         <v>30</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -677,7 +667,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>碗裡的硬幣，倒水以後看起來？</t>
+          <t>🪙 碗裡的硬幣，倒水以後看起來？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -703,10 +693,8 @@
       <c r="G14" t="n">
         <v>30</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -715,7 +703,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>游泳池看起來淺淺的，其實是？</t>
+          <t>🏊 游泳池看起來淺淺的，其實是？</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -731,10 +719,8 @@
       <c r="G15" t="n">
         <v>20</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -743,7 +729,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>看起來淺的游泳池，可以直接跳下去嗎？</t>
+          <t>⚠️ 看起來淺的游泳池，可以直接跳下去嗎？</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -759,10 +745,8 @@
       <c r="G16" t="n">
         <v>20</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H16" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/light-refract/files/R1_折射小測驗_Kahoot匯入.xlsx
+++ b/light-refract/files/R1_折射小測驗_Kahoot匯入.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>✨ 光進到水裡會轉彎，這個叫做？</t>
+          <t>✨ 光進到水裡會在水面折一下，這個叫做？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
